--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0189.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0189.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Vẽ tranh không đủ sống… Cuối cùng thì mấy lời hoa mỹ về nghệ thuật và thỏa mãn tinh thần cũng chẳng giúp ta trả nổi hóa đơn.</t>
+          <t>Vẽ tranh không đủ sống… Cuối cùng thì mấy lời hoa mỹ về nghệ thuật và thỏa mãn tinh thần cũng chẳng giúp tao trả nổi hóa đơn.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>{Male=Chàng trai;Female=Cô gái} trẻ à, cậu có thể giúp tôi mang những bông hoa này đến cho anh ấy được không?</t>
+          <t>{Male=man;Female=lady} trẻ à, cậu có thể giúp tôi mang những bông hoa này đến cho anh ấy được không?</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Nếu không có họ ngăn ta lại, ta đã đích thân đến thăm họ và nói rằng ta chưa bao giờ quên họ.</t>
+          <t>Nếu không có họ ngăn tao lại, tao đã đích thân đến thăm họ và nói rằng tao chưa bao giờ quên họ.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mãi đến bây giờ ta mới biết hắn đến đây mỗi ngày! Ta chỉ muốn thuyết phục hắn quay về Kim Châu thôi, nhưng hắn chẳng thèm nghe. Bực mình thật đấy!</t>
+          <t>Mãi đến bây giờ tao mới biết hắn đến đây mỗi ngày! Tao chỉ muốn thuyết phục hắn quay về Jinzhou thôi, nhưng hắn chẳng thèm nghe. Bực mình thật đấy!</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Này, {Male=chàng trai;Female=cô gái} trẻ! Shiying chắc mừng lắm khi có người đến thăm đấy!</t>
+          <t>Này, {Male=man;Female=lady} trẻ! Shiying chắc mừng lắm khi có người đến thăm đấy!</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Ta sẽ không gây rắc rối đâu. Ta chỉ muốn dành thêm chút thời gian bên họ thôi.</t>
+          <t>Tao sẽ không gây rắc rối đâu. Tao chỉ muốn dành thêm chút thời gian bên họ thôi.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Làm sao tôi biết tên của cậu được? Lạ thật đấy. Xin lỗi, cậu {Male=chàng trai;Female=cô gái} trẻ.</t>
+          <t>Làm sao tôi biết tên của cậu được? Lạ thật đấy. Xin lỗi, cậu {Male=man;Female=lady} trẻ.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Sao cậu biết ta sắp gửi hoa cho bạn bè vậy?</t>
+          <t>Sao cậu biết tao sắp gửi hoa cho bạn bè vậy?</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Thật sao? Ta có làm phiền cậu trước đây à? Xin lỗi, trí nhớ ta càng ngày càng tệ...</t>
+          <t>Thật sao? Tao có làm phiền cậu trước đây à? Xin lỗi, trí nhớ tao càng ngày càng tệ...</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Suýt nữa thì nhầm cậu, xin lỗi. Giờ ta thấy rõ rồi. Cậu là Yao của Bộ Phát Triển à?</t>
+          <t>Suýt nữa thì nhầm cậu, xin lỗi. Giờ tao thấy rõ rồi. Cậu là Yao của Bộ Phát Triển à?</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>V-vâng, cảm ơn cậu đã giúp đỡ.</t>
+          <t>V-vâng, cảm ơn bạn đã giúp đỡ.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Ngày xưa có thể được, nhưng giờ Cao nguyên Desorock quá gần tiền tuyến, người dân không còn được phép lên đó nữa.</t>
+          <t>Ngày xưa có thể được, nhưng giờ Desorock Highland quá gần tiền tuyến, người dân không còn được phép lên đó nữa.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Giao cái gì? Cậu đến đây để báo là đơn đã được duyệt à?!</t>
+          <t>Giao cái gì? Mày đến đây để báo là đơn đã được duyệt à?!</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ta sẽ giúp ngươi tìm họ.</t>
+          <t>Tao sẽ giúp mày tìm họ.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Gì? Đừng có giở trò với ta. Cả đời này, có hai thứ ta tự hào nhất là…</t>
+          <t>Gì? Đừng có giở trò với tao. Cả đời này, có hai thứ tao tự hào nhất là…</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Mỗi khi ta kể cho hắn nghe một câu chuyện cười mới học được, hắn lại cười gượng như thể đã nghe đi nghe lại cả trăm lần rồi!</t>
+          <t>Mỗi khi tao kể cho hắn nghe một câu chuyện cười mới học được, hắn lại cười gượng như thể đã nghe đi nghe lại cả trăm lần rồi!</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Ta gửi tọa độ cho cậu rồi. Như thường lệ, bắt được mấy con lông lá đó thì mang về cho ta nhé. Cảm ơn trước!</t>
+          <t>Tao gửi tọa độ cho cậu rồi. Như thường lệ, bắt được mấy con lông lá đó thì mang về cho tao nhé. Cảm ơn trước!</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Ồ! Chắc hẳn cậu chính là Rover đến hỗ trợ Đội Giải Cứu Mèo rồi!</t>
+          <t>Ồ! Chắc hẳn cậu chính là Vận Mệnh Giả đến hỗ trợ Đội Giải Cứu Mèo rồi!</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tốt quá! Rover như cậu thì lúc nào cũng vậy. Đến lúc đặt tên rồi đấy!</t>
+          <t>Tốt quá! Vận Mệnh Giả như cậu thì lúc nào cũng vậy. Đến lúc đặt tên rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Ta gửi tọa độ cho cậu rồi. Như thường lệ, mang chúng về cho ta khi lấy được nhé. Cảm ơn trước!</t>
+          <t>Tao gửi tọa độ cho cậu rồi. Như thường lệ, mang chúng về cho tao khi lấy được nhé. Cảm ơn trước!</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tốt quá! Rover như cậu thì lúc nào cũng vậy. Đến lúc đặt tên rồi đấy!</t>
+          <t>Tốt quá! Vận Mệnh Giả như cậu thì lúc nào cũng vậy. Đến lúc đặt tên rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Bọn ta trông cậy vào cậu đấy, Rover!</t>
+          <t>Bọn tao trông cậy vào cậu đấy, Rover!</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Nếu cậu không mang theo bên người lúc này. Mình nghĩ cậu có thể tìm thấy vài cái ở &lt;color=Highlight&gt;the waterfall by heading east from the shop&lt;/color&gt; đấy.</t>
+          <t>Nếu cậu không mang theo bên người lúc này. Mình nghĩ cậu có thể tìm thấy vài cái ở &lt;color=Highlight&gt;thác nước phía đông cửa hàng&lt;/color&gt; đấy.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hehe... Dễ ợt. Đó là việc của tụi mình mà. Ta sẽ chăm sóc chúng như mọi khi thôi.</t>
+          <t>Hehe... Dễ ợt. Đó là việc của tụi mình mà. Tao sẽ chăm sóc chúng như mọi khi thôi.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>À, chính Rover đã cứu tất cả bọn họ và thỉnh thoảng còn ghé thăm nữa. Chả trách họ quý {Male=anh ấy;Female=cô ấy} đến thế.</t>
+          <t>À, chính Rover đã cứu tất cả bọn họ và thỉnh thoảng còn ghé thăm nữa. Chả trách họ quý {Male=him;Female=her} đến thế.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Meo hai tiếng nếu ngươi muốn đi cùng ta.</t>
+          <t>Meo hai tiếng nếu mày muốn đi cùng tao.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>...Meow.</t>
+          <t>...Meo.</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ta không chấp nhận lời từ chối đâu... Cậu phải đi với ta!</t>
+          <t>Tao không chấp nhận lời từ chối đâu... Cậu phải đi với tao!</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Haha, cậu trả lời ta kiểu đó là cố tình chứ gì? Cứ như thể đang đóng vai tay sai ấy.</t>
+          <t>Haha, cậu trả lời tao kiểu đó là cố tình chứ gì? Cứ như thể đang đóng vai tay sai ấy.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tôi liên lạc với cậu thay mặt cho Trạm Tuần Tra. Xin lỗi vì yêu cầu đột xuất.</t>
+          <t>Tôi liên lạc với bạn thay mặt cho Trạm Tuần Tra. Xin lỗi vì yêu cầu đột xuất.</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Người cung cấp thông tin của cậu?</t>
+          <t>Người cung cấp thông tin của bạn?</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hắn là tai mắt của ta, mách cho ta mọi tin đồn ngoài phố, giúp ích rất nhiều trong việc phá án.</t>
+          <t>Hắn là tai mắt của tao, mách cho tao mọi tin đồn ngoài phố, giúp ích rất nhiều trong việc phá án.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Của cậu đây.</t>
+          <t>Cậu đến rồi.</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Sau khi con chuột bỏ đi, tôi đến hỏi con mèo: "Sao cậu không bắt nó mà ăn?"</t>
+          <t>Sau khi con chuột bỏ đi, tôi đến hỏi con mèo: "Sao mày không bắt nó mà ăn?"</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Nửa đêm qua, ta thấy hai con mèo này lén lút đi chơi với nhau vui vẻ lắm.</t>
+          <t>Nửa đêm qua, tao thấy hai con mèo này lén lút đi chơi với nhau vui vẻ lắm.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Ừ. Ta thức trắng đêm để viết đoạn này đấy. Nghe thử xem sao.</t>
+          <t>Ừ. Tao thức trắng đêm để viết đoạn này đấy. Nghe thử xem sao.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Và đó là lý do tại sao ta không thể tìm thấy cái kết cho câu chuyện.</t>
+          <t>Và đó là lý do tại sao tao không thể tìm thấy cái kết cho câu chuyện.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Ta sẽ cho ngươi thêm một cơ hội, câu trả lời đúng gần hơn ngươi nghĩ đấy.</t>
+          <t>Tao sẽ cho mày thêm một cơ hội, câu trả lời đúng gần hơn mày nghĩ đấy.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Ta sẽ cho ngươi thêm một cơ hội, câu trả lời đúng gần hơn ngươi nghĩ đấy.</t>
+          <t>Tao sẽ cho mày thêm một cơ hội, câu trả lời đúng gần hơn mày nghĩ đấy.</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Ta đang cố xây dựng một "mô hình truyền tín hiệu thực vật" để xem cây cảnh phản ứng thế nào với các loại âm thanh khác nhau.</t>
+          <t>Tao đang cố xây dựng một "mô hình truyền tín hiệu thực vật" để xem cây cảnh phản ứng thế nào với các loại âm thanh khác nhau.</t>
         </is>
       </c>
     </row>
